--- a/backend/scripts/excel_import_template.xlsx
+++ b/backend/scripts/excel_import_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题库导入" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="题库导入" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="字段说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,9 @@
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -568,10 +570,20 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>real_exam_year</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>external_ref</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
@@ -666,8 +678,16 @@
           <t>platform-original</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>REAL_EXAM</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>sample,main_idea</t>
         </is>
@@ -684,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -874,22 +894,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>external_ref</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>选填；PLATFORM_ORIGINAL / REAL_EXAM / MOCK / COMPILATION，留空按 PLATFORM_ORIGINAL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>real_exam_year</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>选填；仅 source_type=REAL_EXAM 时填，如 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>external_ref</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>选填；英文逗号分隔</t>
         </is>
